--- a/uploads/Inside Racing Apprentices - July Edition.xlsx
+++ b/uploads/Inside Racing Apprentices - July Edition.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://racingvictorialtd057-my.sharepoint.com/personal/s_cunliffe_racingvictoria_net_au/Documents/AAA Strategy &amp; Projects/Inside Racing/Automation - AI/Input Files - Build Example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4262F20-8A8D-4437-A7F1-7A847BCF4201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A6430D89-0652-48A3-AD7C-B545602393AD}"/>
   </bookViews>
